--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="114">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -210,12 +210,6 @@
   </si>
   <si>
     <t>Testare</t>
-  </si>
-  <si>
-    <t>Depanare</t>
-  </si>
-  <si>
-    <t>Re-testare</t>
   </si>
   <si>
     <t>Testare de regresie</t>
@@ -267,60 +261,6 @@
         <family val="2"/>
       </rPr>
       <t>[se va prelua valoarea indicata in raportul de acoperire pentru metoda testata]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#Bugs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="8"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[se va indica numarul de bug-uri identificate prin depanare, la nivelul metodei testate]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#Bugs Fixed </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="8"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[se va completa cu 'da' dupa depanare]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Re-testare </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>[se va completa cu 'da' dupa retestare]</t>
     </r>
   </si>
   <si>
@@ -467,15 +407,9 @@
     </r>
   </si>
   <si>
-    <t>comanda cu produse si stoc suficient</t>
-  </si>
-  <si>
     <t>comanda se finalizeaza</t>
   </si>
   <si>
-    <t>comanda cu un produs care are stoc insuficient</t>
-  </si>
-  <si>
     <t>se arunca exceptie</t>
   </si>
   <si>
@@ -518,20 +452,80 @@
     <t>F02_P05</t>
   </si>
   <si>
-    <t>1 - 2(F) - 3(T) - 4(T) - 5(T) - 3(F) - 8</t>
-  </si>
-  <si>
     <t>1 - 2(F) - 3(T) - (4(T) - 5(F) - 6)* - 4(T) - 5(T) - 3(F) - end</t>
   </si>
   <si>
     <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>F02_TC03</t>
+  </si>
+  <si>
+    <t>F02_TC04</t>
+  </si>
+  <si>
+    <t>F02_TC05</t>
+  </si>
+  <si>
+    <t>1 - 2(F) - 3(T) - 4(T) - 5(F) - 6 - 4(T) - 5(T) - 3(F) - end</t>
+  </si>
+  <si>
+    <t>comanda cu reteta != null care are stoc insuficient</t>
+  </si>
+  <si>
+    <t>comanda cu reteta goala</t>
+  </si>
+  <si>
+    <t>comanda cu reteta care nu e goala si stoc suficient intr un singur lot</t>
+  </si>
+  <si>
+    <t>comanda cu reteta care nu e goala si stoc suficient pe mai multe loturi</t>
+  </si>
+  <si>
+    <t>1,2,4,5,19</t>
+  </si>
+  <si>
+    <t>comanda cu reteta care nu e goala si stoc care nu are ingredientul</t>
+  </si>
+  <si>
+    <t>1,2,4,5,6,7,8,9,10,11,12,18,19</t>
+  </si>
+  <si>
+    <t>reteta: Cafea 30, stoc: Cafea 50</t>
+  </si>
+  <si>
+    <t>stocul se actualizeaza (50 -&gt; 30), fara exceptie</t>
+  </si>
+  <si>
+    <t>passed</t>
+  </si>
+  <si>
+    <t>reteta: Cafea 10, stoc: Cafea 5</t>
+  </si>
+  <si>
+    <t>reteta: Lapte 70, stoc: Lapte 30+50</t>
+  </si>
+  <si>
+    <t>se arunca IllegalStateException</t>
+  </si>
+  <si>
+    <t>stoc1 -&gt; 0, stoc2 -&gt; 10</t>
+  </si>
+  <si>
+    <t>reteta: []</t>
+  </si>
+  <si>
+    <t>reteta: Matcha 10, stoc: nu exista Matcha</t>
+  </si>
+  <si>
+    <t>nu se arunca exceptie, se sare peste bucla interioara</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,13 +569,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,13 +595,6 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -741,7 +721,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -800,21 +780,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1092,19 +1057,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -1126,15 +1078,6 @@
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1215,360 +1158,327 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1964,16 +1874,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="10"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1991,21 +1901,21 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26" t="s">
+      <c r="N6" s="21"/>
+      <c r="O6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P6" s="21" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2014,13 +1924,13 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="26" t="s">
+      <c r="N7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" s="26">
+      <c r="O7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="P7" s="21">
         <v>236</v>
       </c>
     </row>
@@ -2029,44 +1939,44 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="26" t="s">
+      <c r="N8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="P8" s="26">
+      <c r="O8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="21">
         <v>236</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="26" t="s">
+      <c r="N9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="P9" s="26">
+      <c r="O9" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="21">
         <v>236</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B11" s="36" t="s">
-        <v>79</v>
+      <c r="B11" s="30" t="s">
+        <v>74</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2106,361 +2016,353 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="10"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
+      <c r="B3" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="I6" s="54" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="I6" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="Q6" s="54" t="s">
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="Q6" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="I8" s="12" t="s">
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="I8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="71" t="s">
+      <c r="Q8" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="33">
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="27">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="I9" s="37"/>
-      <c r="Q9" s="71" t="s">
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="I9" s="31"/>
+      <c r="Q9" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="33" t="s">
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B10" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="I10" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="62"/>
+      <c r="Q10" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="55"/>
+      <c r="T10" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="65"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B12" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="65"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B13" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="65"/>
+      <c r="Q13" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B14" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="65"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="I15" s="63"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="65"/>
+      <c r="Q15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="I16" s="63"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="65"/>
+      <c r="Q16" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.35">
+      <c r="I17" s="63"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="65"/>
+      <c r="Q17" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.35">
+      <c r="I18" s="63"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="65"/>
+      <c r="Q18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="R18" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="S18" s="56"/>
+      <c r="T18" s="56"/>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.35">
+      <c r="I19" s="63"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="65"/>
+      <c r="Q19" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="R19" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="S19" s="56"/>
+      <c r="T19" s="56"/>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.35">
+      <c r="I20" s="63"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="65"/>
+      <c r="Q20" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="R20" s="56" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B10" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="I10" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="64"/>
-      <c r="Q10" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="71" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10" s="71"/>
-      <c r="T10" s="33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B11" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="67"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B12" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="67"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B13" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="66"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="66"/>
-      <c r="O13" s="67"/>
-      <c r="Q13" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="66"/>
-      <c r="O14" s="67"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="67"/>
-      <c r="Q15" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="R15" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="67"/>
-      <c r="Q16" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-    </row>
-    <row r="17" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="67"/>
-      <c r="Q17" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="S17" s="57"/>
-      <c r="T17" s="57"/>
-    </row>
-    <row r="18" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I18" s="65"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="67"/>
-      <c r="Q18" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R18" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
-    </row>
-    <row r="19" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I19" s="65"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="67"/>
-      <c r="Q19" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="R19" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-    </row>
-    <row r="20" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I20" s="65"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="67"/>
-      <c r="Q20" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="R20" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="56"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I21" s="65"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="67"/>
-      <c r="Q21" s="128"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="65"/>
+      <c r="Q21" s="48"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I22" s="65"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="67"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="65"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="67"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="65"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.35">
-      <c r="I24" s="68"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="70"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="R20:T20"/>
@@ -2476,6 +2378,14 @@
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2513,276 +2423,362 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="10"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="71"/>
+    </row>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.35">
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.35">
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="2:30" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="72" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="45"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="46"/>
+      <c r="AD6" s="46"/>
+    </row>
+    <row r="7" spans="2:30" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="73"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="42"/>
+    </row>
+    <row r="8" spans="2:30" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="73"/>
+      <c r="C8" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="78"/>
+      <c r="F8" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="85"/>
+      <c r="H8" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82"/>
-    </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="I4" s="35"/>
-    </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.35">
-      <c r="B5" s="11"/>
-    </row>
-    <row r="6" spans="2:30" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="52"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="52"/>
-    </row>
-    <row r="7" spans="2:30" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="84"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="48"/>
-    </row>
-    <row r="8" spans="2:30" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="84"/>
-      <c r="C8" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="80"/>
-      <c r="H8" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="80"/>
-      <c r="J8" s="75" t="s">
+      <c r="I8" s="85"/>
+      <c r="J8" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="75" t="s">
+      <c r="K8" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="75" t="s">
+      <c r="L8" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="75" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="75" t="s">
+      <c r="M8" s="82" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" s="82" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="80">
+        <v>0</v>
+      </c>
+      <c r="P8" s="80">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="80">
+        <v>2</v>
+      </c>
+      <c r="R8" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="74"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
+    </row>
+    <row r="10" spans="2:30" ht="62" x14ac:dyDescent="0.35">
+      <c r="B10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="T10" s="39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="O8" s="73">
-        <v>0</v>
-      </c>
-      <c r="P8" s="73">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="73">
-        <v>2</v>
-      </c>
-      <c r="R8" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="T8" s="73" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="2:30" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="85"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="76"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="74"/>
-      <c r="T9" s="74"/>
-    </row>
-    <row r="10" spans="2:30" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="D11" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+    </row>
+    <row r="12" spans="2:30" ht="62" x14ac:dyDescent="0.35">
+      <c r="B12" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="T10" s="45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="2:30" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-    </row>
-    <row r="12" spans="2:30" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="19"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="39"/>
+      <c r="S12" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="T12" s="39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" ht="31" x14ac:dyDescent="0.35">
+      <c r="B13" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+    </row>
+    <row r="14" spans="2:30" ht="62" x14ac:dyDescent="0.35">
+      <c r="B14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="39"/>
+      <c r="S14" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="T14" s="16"/>
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.35">
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E7:E9"/>
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="K8:K9"/>
@@ -2797,6 +2793,13 @@
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2808,422 +2811,271 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
+  <dimension ref="B1:I16"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.26953125" customWidth="1"/>
+    <col min="5" max="5" width="40.08984375" customWidth="1"/>
+    <col min="6" max="6" width="45.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="D1" s="54" t="s">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="10"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="56"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="91" t="s">
+      <c r="E1" s="52"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="92" t="s">
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="D4" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="94" t="s">
+      <c r="F4" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="95"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="93"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="104"/>
+      <c r="G4" s="108"/>
+    </row>
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="106"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="113"/>
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="97"/>
-      <c r="K5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="20">
+    <row r="6" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="17">
         <v>9</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="109" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="105" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="106"/>
-      <c r="K6" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="20">
+      <c r="E6" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="17">
         <v>10</v>
       </c>
-      <c r="C7" s="98"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="20">
-        <v>5</v>
-      </c>
-      <c r="F7" s="20">
-        <v>6</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="95"/>
-      <c r="K7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="20">
+      <c r="E7" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="17">
         <v>11</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="20">
+      <c r="C8" s="109"/>
+      <c r="D8" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="17">
         <v>12</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C9" s="109"/>
+      <c r="D9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="9" t="s">
-        <v>19</v>
+      <c r="C10" s="110"/>
+      <c r="D10" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="2:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="107" t="s">
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="2:9" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="89" t="s">
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="90"/>
-      <c r="H13" s="107" t="s">
+      <c r="I13" s="91"/>
+    </row>
+    <row r="14" spans="2:9" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="114" t="s">
+      <c r="C14" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="115"/>
-    </row>
-    <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="113" t="s">
+      <c r="D14" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="E14" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="F14" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="119" t="s">
+      <c r="G14" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="121" t="s">
+      <c r="H14" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="123" t="s">
+      <c r="I14" s="97" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="124" t="s">
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="92"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="98"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="21">
+        <f>SUM(C16:D16)</f>
+        <v>12</v>
+      </c>
+      <c r="C16" s="20">
+        <v>12</v>
+      </c>
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="114">
+        <v>1</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="115">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="117" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="126" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="M14" s="112" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="101" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="116"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="121"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="26">
-        <f>SUM(C16:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="23">
-        <v>0</v>
-      </c>
-      <c r="D16" s="23">
-        <v>0</v>
-      </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="26">
-        <f>SUM(J16:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="23">
-        <v>0</v>
-      </c>
-      <c r="K16" s="27">
-        <v>0</v>
-      </c>
-      <c r="L16" s="28"/>
-      <c r="M16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="N16" s="29">
+      <c r="I16" s="23">
         <f>C16</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="M13:N13"/>
+  <mergeCells count="18">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
+    <mergeCell ref="I14:I15"/>
     <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="J14:J15"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="H13:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3231,26 +3083,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="08d9df77a39a0ee87f79f9436c57bbce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" xmlns:ns3="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="03dd79bc1474883a2d909db85c328b07" ns2:_="" ns3:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -3439,32 +3271,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B359A3C-84EA-4FDD-BB5C-023A91F35CC6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3481,4 +3308,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>